--- a/Planilha Inteligente e IA.xlsx
+++ b/Planilha Inteligente e IA.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cris_\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBC1A02-642B-4BC2-B805-B598903DEA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF06239C-7C8B-4825-AF8A-8EB025737424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" tabRatio="153" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DATA" sheetId="1" r:id="rId1"/>
-    <sheet name="CONTROLLER" sheetId="2" r:id="rId2"/>
-    <sheet name="CAIXINHA" sheetId="4" r:id="rId3"/>
+    <sheet name="DATA" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="CONTROLLER" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="CAIXINHA" sheetId="4" state="hidden" r:id="rId3"/>
     <sheet name="DASHBOARD" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="36" r:id="rId5"/>
+    <pivotCache cacheId="24" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -354,9 +354,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="&quot;R$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -370,6 +370,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="0"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -411,7 +418,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -423,7 +430,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -431,8 +438,11 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -441,13 +451,19 @@
   </cellStyles>
   <dxfs count="15">
     <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -466,7 +482,10 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="166" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <numFmt numFmtId="164" formatCode="&quot;R$&quot;\ #,##0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -478,6 +497,16 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -531,30 +560,11 @@
         <horizontal/>
       </border>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="SlicerStyleDark1 2" pivot="0" table="0" count="10" xr9:uid="{C9AA7A34-D088-4CC9-8AF8-B1ADCB2458A0}">
-      <tableStyleElement type="wholeTable" dxfId="8"/>
-      <tableStyleElement type="headerRow" dxfId="7"/>
+      <tableStyleElement type="wholeTable" dxfId="14"/>
+      <tableStyleElement type="headerRow" dxfId="13"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -4080,6 +4090,124 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>147638</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1256306" cy="405432"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="CaixaDeTexto 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3327B4CC-7820-69A8-0BF3-F02D2BF89F7A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1443038" y="190500"/>
+          <a:ext cx="1256306" cy="405432"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="2000" kern="1200">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Black" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Caixinha</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>557213</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>80963</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Gráfico 3" descr="Cofrinho estrutura de tópicos">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE10196F-E997-A66D-32C7-A7CAEB762AFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="400050" y="0"/>
+          <a:ext cx="804863" cy="804863"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -4106,8 +4234,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1413782" y="5627975"/>
-          <a:ext cx="11845018" cy="3825586"/>
+          <a:off x="1413782" y="5554156"/>
+          <a:ext cx="11866449" cy="3775580"/>
           <a:chOff x="1713820" y="4184938"/>
           <a:chExt cx="8446077" cy="3825586"/>
         </a:xfrm>
@@ -4401,8 +4529,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1337582" y="1002487"/>
-          <a:ext cx="6587218" cy="4336276"/>
+          <a:off x="1337582" y="990581"/>
+          <a:ext cx="6599124" cy="4279126"/>
           <a:chOff x="1713820" y="240487"/>
           <a:chExt cx="4574721" cy="3675648"/>
         </a:xfrm>
@@ -4675,16 +4803,16 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>14285</xdr:rowOff>
+      <xdr:rowOff>14284</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1228725</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>76199</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="37" name="MÊS">
@@ -4707,7 +4835,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -4883,7 +5011,7 @@
       <xdr:grpSpPr>
         <a:xfrm>
           <a:off x="1323294" y="0"/>
-          <a:ext cx="12245069" cy="895350"/>
+          <a:ext cx="12267692" cy="885825"/>
           <a:chOff x="1323294" y="0"/>
           <a:chExt cx="12792075" cy="895350"/>
         </a:xfrm>
@@ -5348,8 +5476,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="8253412" y="1054912"/>
-          <a:ext cx="5010151" cy="4464826"/>
+          <a:off x="8265318" y="1043006"/>
+          <a:ext cx="5019676" cy="4405295"/>
           <a:chOff x="6457949" y="1002525"/>
           <a:chExt cx="4638676" cy="3805237"/>
         </a:xfrm>
@@ -5621,7 +5749,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Cristiane Coelho Reindel" refreshedDate="45669.931111226855" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="30" xr:uid="{F00E47F6-EDC0-4CA0-AC29-709227DADE59}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Cristiane Coelho Reindel" refreshedDate="45669.960127893515" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="30" xr:uid="{F00E47F6-EDC0-4CA0-AC29-709227DADE59}">
   <cacheSource type="worksheet">
     <worksheetSource name="Tbl_operations"/>
   </cacheSource>
@@ -5678,7 +5806,7 @@
     <cacheField name="DESCRIÇÃO" numFmtId="0">
       <sharedItems/>
     </cacheField>
-    <cacheField name="VALOR" numFmtId="166">
+    <cacheField name="VALOR" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="229.18" maxValue="4810.4799999999996"/>
     </cacheField>
     <cacheField name="OPERAÇÃO BANCÁRIA" numFmtId="0">
@@ -6002,11 +6130,27 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2702939A-4658-42D7-99C1-87B1AC0041E3}" name="Tabela dinâmica2" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2702939A-4658-42D7-99C1-87B1AC0041E3}" name="Tabela dinâmica2" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
   <location ref="E4:F12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField numFmtId="14" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0">
+      <items count="13">
+        <item x="0"/>
+        <item x="10"/>
+        <item x="6"/>
+        <item x="11"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="8"/>
+        <item x="4"/>
+        <item x="9"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item x="7"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField axis="axisPage" showAll="0">
       <items count="3">
         <item x="1"/>
@@ -6040,7 +6184,7 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="166" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
@@ -6080,7 +6224,7 @@
     <pageField fld="2" item="0" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Soma de VALOR" fld="5" baseField="0" baseItem="0" numFmtId="166"/>
+    <dataField name="Soma de VALOR" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <chartFormats count="4">
     <chartFormat chart="0" format="0" series="1">
@@ -6133,7 +6277,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D06CED31-0C11-49C8-9B0C-817337452047}" name="Tabela dinâmica1" cacheId="36" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D06CED31-0C11-49C8-9B0C-817337452047}" name="Tabela dinâmica1" cacheId="24" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="A4:B11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField numFmtId="14" showAll="0"/>
@@ -6187,7 +6331,7 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
-    <pivotField dataField="1" numFmtId="166" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
@@ -6224,7 +6368,7 @@
     <pageField fld="2" item="1" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Soma de VALOR" fld="5" baseField="0" baseItem="0" numFmtId="166"/>
+    <dataField name="Soma de VALOR" fld="5" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="7" format="3" series="1">
@@ -6253,6 +6397,7 @@
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_MÊS" xr10:uid="{0C92DAD0-915C-4178-A02F-3CBDBA6AAEE1}" sourceName="MÊS">
   <pivotTables>
     <pivotTable tabId="2" name="Tabela dinâmica1"/>
+    <pivotTable tabId="2" name="Tabela dinâmica2"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="774799832">
@@ -6260,15 +6405,15 @@
         <i x="0" s="1"/>
         <i x="10" s="1"/>
         <i x="6" s="1"/>
+        <i x="11" s="1"/>
         <i x="3" s="1"/>
         <i x="1" s="1"/>
+        <i x="8" s="1"/>
         <i x="4" s="1"/>
         <i x="9" s="1"/>
         <i x="5" s="1"/>
         <i x="2" s="1"/>
         <i x="7" s="1"/>
-        <i x="11" s="1" nd="1"/>
-        <i x="8" s="1" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -6282,19 +6427,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{049DDA5A-03E2-4F90-9F8F-15ACDF7B6C00}" name="Tbl_operations" displayName="Tbl_operations" ref="A1:H31" totalsRowShown="0" headerRowDxfId="11" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{049DDA5A-03E2-4F90-9F8F-15ACDF7B6C00}" name="Tbl_operations" displayName="Tbl_operations" ref="A1:H31" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="A1:H31" xr:uid="{049DDA5A-03E2-4F90-9F8F-15ACDF7B6C00}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{A58F5D0A-5D36-4A23-AB8A-D926A1A029C5}" name="DATA" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{3CE6B766-3C44-4303-9418-72EF7E7E04FF}" name="MÊS" dataDxfId="6">
+    <tableColumn id="8" xr3:uid="{3CE6B766-3C44-4303-9418-72EF7E7E04FF}" name="MÊS" dataDxfId="9">
       <calculatedColumnFormula>MONTH(A2)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{D301E30C-00FE-435F-ADB2-FE6B9C9D9AA0}" name="TIPO " dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{02EF2FAD-99FF-4029-A95C-F36D73F45C61}" name="CATEGORIA" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{9FB1D4C5-676C-40C3-99B3-8786FEAFC4A2}" name="DESCRIÇÃO" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{D7AB04E2-06B3-488D-8B67-CFB4B02271DB}" name="VALOR" dataDxfId="3" dataCellStyle="Moeda"/>
+    <tableColumn id="2" xr3:uid="{D301E30C-00FE-435F-ADB2-FE6B9C9D9AA0}" name="TIPO " dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{02EF2FAD-99FF-4029-A95C-F36D73F45C61}" name="CATEGORIA" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{9FB1D4C5-676C-40C3-99B3-8786FEAFC4A2}" name="DESCRIÇÃO" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{D7AB04E2-06B3-488D-8B67-CFB4B02271DB}" name="VALOR" dataDxfId="5"/>
     <tableColumn id="6" xr3:uid="{DF406410-E102-4201-A495-25696CB26AC1}" name="OPERAÇÃO BANCÁRIA" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{EE37B62E-9039-4104-B201-0591AA07EBB0}" name="STATUS" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{EE37B62E-9039-4104-B201-0591AA07EBB0}" name="STATUS" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7594,6 +7739,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91F73EDA-9E2B-47AC-8A22-95E7B1031143}">
+  <sheetPr>
+    <tabColor theme="0" tint="-0.249977111117893"/>
+  </sheetPr>
   <dimension ref="A1:U37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -7602,7 +7750,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="7"/>
+      <c r="A1" s="12"/>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="7"/>
@@ -7894,8 +8042,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7923,26 +8072,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="851b35d3-0456-4d6a-bc2f-da927e91d158">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="19483571-f922-4e8e-9c1c-26f0a2252132" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010001E48B58A68BE64E9120D347E3E06B3A" ma:contentTypeVersion="19" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="2f90046ec77328b7f86417d2e03b3d33">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="851b35d3-0456-4d6a-bc2f-da927e91d158" xmlns:ns3="19483571-f922-4e8e-9c1c-26f0a2252132" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c815006ac2d4f05ee97fdd57e40d8e38" ns2:_="" ns3:_="">
     <xsd:import namespace="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
@@ -8197,10 +8326,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="851b35d3-0456-4d6a-bc2f-da927e91d158">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="19483571-f922-4e8e-9c1c-26f0a2252132" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4963D8E4-1D6C-4FCF-8D1D-F56D49A3BA19}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51DA261A-E008-49B4-91DC-52FE5A91438B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
+    <ds:schemaRef ds:uri="19483571-f922-4e8e-9c1c-26f0a2252132"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8217,20 +8377,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51DA261A-E008-49B4-91DC-52FE5A91438B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4963D8E4-1D6C-4FCF-8D1D-F56D49A3BA19}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
-    <ds:schemaRef ds:uri="19483571-f922-4e8e-9c1c-26f0a2252132"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>